--- a/report_forms/043_service_record_form--report_forms.xlsx
+++ b/report_forms/043_service_record_form--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -792,8 +792,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_9.1,_'name':_'monthly',_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 9.1, 'name': 'monthly', 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_9.2,_'name':_'quarterly',_'label':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 9.2, 'name': 'quarterly', 'label': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_9.3,_'name':_'semi_annual',_'label':_'semi-annual'}</t>
+          <t>semi-annual</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 9.3, 'name': 'semi_annual', 'label': 'Semi-annual'}</t>
+          <t>Semi-annual</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_9.4,_'name':_'yearly',_'label':_'yearly'}</t>
+          <t>yearly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 9.4, 'name': 'yearly', 'label': 'Yearly'}</t>
+          <t>Yearly</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_10.1,_'name':_'oil_service',_'label':_'oil_service'}</t>
+          <t>oil_service</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 10.1, 'name': 'Oil Service', 'label': 'Oil Service'}</t>
+          <t>Oil Service</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_10.2,_'name':_'tire_service',_'label':_'tire_service'}</t>
+          <t>tire_service</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 10.2, 'name': 'Tire Service', 'label': 'Tire Service'}</t>
+          <t>Tire Service</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_10.3,_'name':_'maintenance_service',_'label':_'maintenance_service'}</t>
+          <t>maintenance_service</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 10.3, 'name': 'Maintenance Service', 'label': 'Maintenance Service'}</t>
+          <t>Maintenance Service</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_10.4,_'name':_'inspection_service',_'label':_'inspection_service'}</t>
+          <t>inspection_service</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 10.4, 'name': 'Inspection Service', 'label': 'Inspection Service'}</t>
+          <t>Inspection Service</t>
         </is>
       </c>
     </row>
